--- a/salesforce_forms/006_social_media_contest_registration_form--salesforce_forms.xlsx
+++ b/salesforce_forms/006_social_media_contest_registration_form--salesforce_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C34"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -1262,17 +1262,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>social_media_type_choices</t>
+          <t>social_media_platform_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>snapchat</t>
+          <t>facebook</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>snapchat</t>
+          <t>facebook</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>facebook</t>
+          <t>twitter</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>facebook</t>
+          <t>twitter</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>twitter</t>
+          <t>snapchat</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>twitter</t>
+          <t>snapchat</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>snapchat</t>
+          <t>youtube</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>snapchat</t>
+          <t>youtube</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>youtube</t>
+          <t>tiktok</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>youtube</t>
+          <t>tiktok</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>tiktok</t>
+          <t>pinterest</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>tiktok</t>
+          <t>pinterest</t>
         </is>
       </c>
     </row>
@@ -1369,29 +1369,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>pinterest</t>
+          <t>reddit</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>pinterest</t>
+          <t>reddit</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>social_media_platform_choices</t>
+          <t>prize_type_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>reddit</t>
+          <t>gift_card</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>reddit</t>
+          <t>gift card</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>gift_card</t>
+          <t>gift_card_and_other</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>gift_card</t>
+          <t>gift card and other</t>
         </is>
       </c>
     </row>
@@ -1420,29 +1420,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gift_card_and_other</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>gift_card_and_other</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>prize_type_choices</t>
+          <t>participant_agreement_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1454,29 +1454,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>participant_agreement_choices</t>
+          <t>participant_agreement_holds_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1488,29 +1488,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>participant_agreement_holds_choices</t>
+          <t>participant_language_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>english</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>english</t>
+          <t>french</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>english</t>
+          <t>french</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>french</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>french</t>
+          <t>spanish</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>spanish</t>
+          <t>german</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>spanish</t>
+          <t>german</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>german</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>german</t>
+          <t>chinese</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>arabic</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>arabic</t>
         </is>
       </c>
     </row>
@@ -1607,29 +1607,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>arabic</t>
+          <t>portuguese</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>arabic</t>
+          <t>portuguese</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>participant_language_choices</t>
+          <t>participant_gender_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>portuguese</t>
+          <t>male</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>portuguese</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -1658,27 +1658,10 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
-        <is>
-          <t>female</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>participant_gender_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
         <is>
           <t>other</t>
         </is>
